--- a/week-2/Danh Sach Thanh Vien Nhom.xlsx
+++ b/week-2/Danh Sach Thanh Vien Nhom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Big Boss\Desktop\nhom26 git\uit-artificial-intelligence\week-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A5C661-FC89-493E-AFD0-1F92382FBA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4709661B-78CE-4473-8268-802C02ED629F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{590C0C11-1AF1-4B6D-BF5E-40873E33DE0B}"/>
   </bookViews>
@@ -92,9 +92,6 @@
     <t>Bài 1.11</t>
   </si>
   <si>
-    <t>DANH SÁCH THÀNH VIÊN NHÓM 8 (NHÓM 6 cũ)</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -114,6 +111,9 @@
       </rPr>
       <t xml:space="preserve"> https://github.com/dinhsst/uit-artificial-intelligence/tree/main/week-2	</t>
     </r>
+  </si>
+  <si>
+    <t>DANH SÁCH THÀNH VIÊN NHÓM 8 (NHÓM 26 cũ)</t>
   </si>
 </sst>
 </file>
@@ -218,12 +218,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -231,7 +228,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -586,144 +583,144 @@
     <col min="5" max="5" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
+    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="3">
         <v>26410020</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>26410010</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>26410105</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="3">
         <v>26410058</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="3">
         <v>26410083</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="3">
         <v>26410008</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="7"/>
     </row>
     <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
+      <c r="A9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
